--- a/artfynd/A 21104-2024 artfynd.xlsx
+++ b/artfynd/A 21104-2024 artfynd.xlsx
@@ -1446,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119520658</v>
+        <v>119520745</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,31 +1458,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>789110</v>
+        <v>788982</v>
       </c>
       <c r="R9" t="n">
-        <v>7290739</v>
+        <v>7290827</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119520745</v>
+        <v>119520666</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>82305</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788982</v>
+        <v>789092</v>
       </c>
       <c r="R10" t="n">
-        <v>7290827</v>
+        <v>7290736</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119520666</v>
+        <v>119520658</v>
       </c>
       <c r="B11" t="n">
-        <v>82305</v>
+        <v>79636</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,31 +1678,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789092</v>
+        <v>789110</v>
       </c>
       <c r="R11" t="n">
-        <v>7290736</v>
+        <v>7290739</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 21104-2024 artfynd.xlsx
+++ b/artfynd/A 21104-2024 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119520599</v>
+        <v>119520713</v>
       </c>
       <c r="B3" t="n">
-        <v>82305</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,27 +801,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>789099</v>
+        <v>788997</v>
       </c>
       <c r="R3" t="n">
-        <v>7290711</v>
+        <v>7290789</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på två sälgar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119520713</v>
+        <v>119520676</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>82305</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,27 +916,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -942,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788997</v>
+        <v>789052</v>
       </c>
       <c r="R4" t="n">
-        <v>7290789</v>
+        <v>7290780</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,11 +983,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>på två sälgar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119520676</v>
+        <v>119520599</v>
       </c>
       <c r="B5" t="n">
         <v>82305</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>789052</v>
+        <v>789099</v>
       </c>
       <c r="R5" t="n">
-        <v>7290780</v>
+        <v>7290711</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21104-2024 artfynd.xlsx
+++ b/artfynd/A 21104-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119520866</v>
+        <v>119520670</v>
       </c>
       <c r="B2" t="n">
         <v>82305</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788971</v>
+        <v>789074</v>
       </c>
       <c r="R2" t="n">
-        <v>7290846</v>
+        <v>7290746</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119520713</v>
+        <v>119520866</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>82305</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,27 +801,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788997</v>
+        <v>788971</v>
       </c>
       <c r="R3" t="n">
-        <v>7290789</v>
+        <v>7290846</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +868,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på två sälgar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119520676</v>
+        <v>119520764</v>
       </c>
       <c r="B4" t="n">
         <v>82305</v>
@@ -947,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789052</v>
+        <v>788972</v>
       </c>
       <c r="R4" t="n">
-        <v>7290780</v>
+        <v>7290843</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1120,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119520670</v>
+        <v>119520745</v>
       </c>
       <c r="B6" t="n">
-        <v>82305</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>789074</v>
+        <v>788982</v>
       </c>
       <c r="R6" t="n">
-        <v>7290746</v>
+        <v>7290827</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119520764</v>
+        <v>119520658</v>
       </c>
       <c r="B7" t="n">
-        <v>82305</v>
+        <v>79636</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,31 +1237,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1277,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788972</v>
+        <v>789110</v>
       </c>
       <c r="R7" t="n">
-        <v>7290843</v>
+        <v>7290739</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119520587</v>
+        <v>119520607</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,29 +1347,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1383,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>789113</v>
+        <v>789119</v>
       </c>
       <c r="R8" t="n">
-        <v>7290693</v>
+        <v>7290720</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119520745</v>
+        <v>119520704</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,27 +1461,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1493,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788982</v>
+        <v>789021</v>
       </c>
       <c r="R9" t="n">
-        <v>7290827</v>
+        <v>7290799</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119520666</v>
+        <v>119520587</v>
       </c>
       <c r="B10" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,29 +1571,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1603,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>789092</v>
+        <v>789113</v>
       </c>
       <c r="R10" t="n">
-        <v>7290736</v>
+        <v>7290693</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119520658</v>
+        <v>119520676</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
+        <v>82305</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,31 +1673,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1713,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789110</v>
+        <v>789052</v>
       </c>
       <c r="R11" t="n">
-        <v>7290739</v>
+        <v>7290780</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119520738</v>
+        <v>119520713</v>
       </c>
       <c r="B12" t="n">
-        <v>82305</v>
+        <v>79607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,27 +1787,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1823,10 +1818,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789006</v>
+        <v>788997</v>
       </c>
       <c r="R12" t="n">
-        <v>7290822</v>
+        <v>7290789</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,6 +1854,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>på två sälgar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119520704</v>
+        <v>119520738</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,27 +1902,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789021</v>
+        <v>789006</v>
       </c>
       <c r="R13" t="n">
-        <v>7290799</v>
+        <v>7290822</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2106,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119520607</v>
+        <v>119520666</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>82305</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2118,31 +2118,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789119</v>
+        <v>789092</v>
       </c>
       <c r="R15" t="n">
-        <v>7290720</v>
+        <v>7290736</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
